--- a/7. CALIBRACION NTC - PTC/mediciones.xlsx
+++ b/7. CALIBRACION NTC - PTC/mediciones.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bremdows\UNSAAC\SEMESTRE X\LABORATORIO DE INSTRUMENTACION\lab-instrumentacion\7. CALIBRACION NTC - PTC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1D7A5F-6922-444F-B2D0-9202F61178FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E567ACE8-7F65-4C6E-BAA6-E86BCBFA4BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{AB4826B5-7769-4DA6-B8E3-44EA4D9375BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>PTC Vo</t>
   </si>
@@ -66,6 +67,12 @@
   </si>
   <si>
     <t>Vi</t>
+  </si>
+  <si>
+    <t>1/T [K°]</t>
+  </si>
+  <si>
+    <t>Ln(RNTCK)</t>
   </si>
 </sst>
 </file>
@@ -109,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -117,6 +124,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1061,6 +1071,98 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.13955119281610306"/>
+                  <c:y val="1.0220871828247338E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Hoja1!$A$2:$A$15</c:f>
@@ -1733,6 +1835,1369 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Ln(R NTC K) vs 1/T [K-1]</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.0830534556932167E-2"/>
+                  <c:y val="0.28439635535307517"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$19:$A$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>3.3898305084745762E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3726812816188868E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3557046979865771E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3388981636060101E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.3222591362126247E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3057851239669421E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.2894736842105261E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.2733224222585926E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.2573289902280132E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.2414910858995136E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.2258064516129032E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.2102728731942215E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.1948881789137379E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.1796502384737681E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$19:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>9.218222372398305</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.149501424774348</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0823961072210952</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.0203218370411804</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.9564018817343172</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.8936238829944401</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.824383730256061</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.764736453263188</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.6988845093288027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.6363036896901466</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.5802039281417688</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.5160599689169363</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.4516238940500461</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.3901830696529469</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F207-4E13-A280-6821B71CD635}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="551556352"/>
+        <c:axId val="551557312"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="551556352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="551557312"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="551557312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="551556352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>R - T (PT100)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.18306188236537546"/>
+                  <c:y val="0.13069774643740131"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$2:$A$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$G$2:$G$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>109.31507056451613</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.59521169354839</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>110.01542338709679</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110.45564516129035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110.93588709677418</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>111.37610887096776</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111.71628024193548</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>112.15650201612905</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>112.57671370967743</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>113.01693548387097</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>113.41713709677418</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>113.85735887096773</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>114.3576108870968</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>114.85786290322579</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B1F6-48D2-BEF5-925374082DCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="804902543"/>
+        <c:axId val="804916943"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="804902543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="15"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="804916943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="804916943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="804902543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>R - T (NTC)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.22846087866467671"/>
+                  <c:y val="-7.5708357401270784E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-PE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$A$2:$A$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$D$2:$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>10079.131451612902</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9409.7477419354836</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8799.0241935483882</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8269.4380645161291</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7757.3951612903229</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7285.3727419354836</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6798</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6404.3738709677409</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5996.2197580645161</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5632.4719354838717</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5325.1913709677419</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4994.3370967741939</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4682.6707258064516</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4403.623790322581</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-DE73-4133-B024-7291173D60D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="804903983"/>
+        <c:axId val="804919343"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="804903983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="804919343"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="804919343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="804903983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1893,6 +3358,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3957,20 +5542,1568 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>464820</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3997,16 +7130,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>411480</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4033,16 +7166,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4069,16 +7202,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>388620</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4098,6 +7231,123 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F4262E0-01DF-286B-7F8F-2DC5761344B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9493B484-359C-4208-9520-096E0AB2096D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>784860</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47F0B536-B614-4C35-B607-00303834D994}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4403,7 +7653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F797930-0F9A-4398-90A1-E2D86F0E61E7}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -4500,7 +7750,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <f t="shared" ref="A4:A24" si="2">A3+1.5</f>
+        <f t="shared" ref="A4:A14" si="2">A3+1.5</f>
         <v>25</v>
       </c>
       <c r="B4" s="3">
@@ -4809,7 +8059,169 @@
         <v>114.85786290322579</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f>1/(273+A2)</f>
+        <v>3.3898305084745762E-3</v>
+      </c>
+      <c r="B19">
+        <f>LN(D2)</f>
+        <v>9.218222372398305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" ref="A20:A35" si="3">1/(273+A3)</f>
+        <v>3.3726812816188868E-3</v>
+      </c>
+      <c r="B20">
+        <f t="shared" ref="B20:B34" si="4">LN(D3)</f>
+        <v>9.149501424774348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="3"/>
+        <v>3.3557046979865771E-3</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="4"/>
+        <v>9.0823961072210952</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="3"/>
+        <v>3.3388981636060101E-3</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="4"/>
+        <v>9.0203218370411804</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="3"/>
+        <v>3.3222591362126247E-3</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="4"/>
+        <v>8.9564018817343172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="3"/>
+        <v>3.3057851239669421E-3</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="4"/>
+        <v>8.8936238829944401</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="3"/>
+        <v>3.2894736842105261E-3</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="4"/>
+        <v>8.824383730256061</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="3"/>
+        <v>3.2733224222585926E-3</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="4"/>
+        <v>8.764736453263188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="3"/>
+        <v>3.2573289902280132E-3</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="4"/>
+        <v>8.6988845093288027</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="3"/>
+        <v>3.2414910858995136E-3</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="4"/>
+        <v>8.6363036896901466</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="3"/>
+        <v>3.2258064516129032E-3</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="4"/>
+        <v>8.5802039281417688</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="3"/>
+        <v>3.2102728731942215E-3</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="4"/>
+        <v>8.5160599689169363</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="3"/>
+        <v>3.1948881789137379E-3</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="4"/>
+        <v>8.4516238940500461</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="3"/>
+        <v>3.1796502384737681E-3</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="4"/>
+        <v>8.3901830696529469</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E3C1C2-D7AA-461B-A5F6-AB4BC4820A7D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
